--- a/formatos/Plantillas_tabulares_curso_IA.xlsx
+++ b/formatos/Plantillas_tabulares_curso_IA.xlsx
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1321,6 +1321,8 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1384,6 +1386,16 @@
           <t>Notas y salvedades</t>
         </is>
       </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Confianza según el equipo revisor</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>¿Resistió la verificación?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1411,7 +1423,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Copilot en Word, anclado al documento</t>
+          <t>Copilot Chat con el archivo adjunto</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1429,6 +1441,8 @@
           <t>Los otros dos programas aceptan además constancia de residencia municipal. La diferencia se documenta en las filas 2 y 3.</t>
         </is>
       </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -1440,6 +1454,8 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="7" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -1451,6 +1467,8 @@
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="7" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1462,6 +1480,8 @@
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="7" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -1473,6 +1493,8 @@
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="7" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1484,6 +1506,8 @@
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="7" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1495,6 +1519,8 @@
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="7" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1506,6 +1532,8 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="7" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1517,6 +1545,8 @@
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="7" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1528,6 +1558,8 @@
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="7" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1539,6 +1571,8 @@
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="7" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1550,6 +1584,8 @@
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="7" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1561,6 +1597,8 @@
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="7" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1572,6 +1610,8 @@
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="7" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1583,6 +1623,8 @@
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="7" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1594,6 +1636,8 @@
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="7" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1605,6 +1649,8 @@
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="7" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1616,6 +1662,8 @@
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="7" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1627,6 +1675,8 @@
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="7" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1638,6 +1688,8 @@
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="7" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1649,6 +1701,8 @@
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="7" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1660,6 +1714,8 @@
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="7" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1671,6 +1727,8 @@
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="7" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1682,6 +1740,8 @@
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="7" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1693,6 +1753,8 @@
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="7" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1704,6 +1766,8 @@
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="7" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1715,6 +1779,8 @@
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="7" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1726,6 +1792,8 @@
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="7" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1737,6 +1805,8 @@
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="7" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1748,6 +1818,8 @@
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="7" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1759,10 +1831,87 @@
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="7" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Paso 4. Los dos números de la medición cruzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Cuántas de las tres verificadas resistieron</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>En fracción: 3 de 3, 2 de 3, 1 de 3 o 0 de 3. No es un porcentaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>a = en cuántas de las seis filas coincidió el nivel de confianza</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Su equipo: filas en alta, en media y en baja</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Equipo revisor: filas en alta, en media y en baja</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>S = suma, nivel por nivel, del conteo de un equipo por el del otro</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>κ = (6a − S) / (36 − S)</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Si a = 6 y S = 36 la fórmula queda 0/0: kappa no definida, no acuerdo perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Alcance declarado</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Seis filas y tres verificaciones ilustran la mecánica sobre su propio trabajo; no estiman la calidad de la matriz.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A2:K3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="H7:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Alta significa dos o más fuentes independientes. Media significa una sola fuente directa. Baja significa evidencia indirecta o inferida." type="list">

--- a/formatos/Plantillas_tabulares_curso_IA.xlsx
+++ b/formatos/Plantillas_tabulares_curso_IA.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Copilot en Word</t>
+          <t>Copilot Chat con el archivo adjunto</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
